--- a/task5_conditional_advice/output/annotation_template.xlsx
+++ b/task5_conditional_advice/output/annotation_template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,178 +488,178 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>故宫_travelog_2_adv_0001</t>
+          <t>泰山_travelog_3_adv_0001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>张伯礼同时提醒:要是要回家过年,特定要严峻遵守防疫要求,最好是点对点,不要过多聚首.</t>
+          <t>11:30:从唐摩崖出发,步行5分钟至玉皇顶餐厅,用餐45分钟(11:35-12:20),人均40元(推荐泰山炒鸡、小米粥),休整10分钟至12:30.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>要回家过年</t>
+          <t>步行5分钟至玉皇顶餐厅</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>最好是点对点,不要过多聚首</t>
+          <t>推荐泰山炒鸡、小米粥),休整10分钟至12:30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0001</t>
+          <t>泰山_travelog_4_adv_0001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>看完升旗后可以在天安门广场上转转,等到8点的时候,可以在天安门广场去排队参观毛主席纪念堂.</t>
+          <t>层级1(整体):3天2晚深度环线(基于官方路线优化,分体能段+文化分支) 层级2(每日结构):核心段+休整段+小众文化分支段 层级3(时段细分):清晨/上午/中午/下午/傍晚,含停留时长+体能建议+文化讲解.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>看完升旗后可以在天安门广场上转转,等到8点</t>
+          <t>含停留时长+体能</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>time_duration</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>可以在天安门广场去排队参观毛主席纪念堂</t>
+          <t>建议+文化讲解</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0002</t>
+          <t>西湖_travelog_1_adv_0001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>出来后你就从天安门广场的地下通道到天安门城楼附近,你可以到天安门城楼上去看看,下来后你一直往里面走,就是故宫的午门,沿着中轴线向北游览三大殿,从神武门出来,对面就是景山公园,从景山公园的西 起了个大早,飞机11:00左右到达北京机场,出机场坐了机场大巴,16元一张票.</t>
+          <t>节假日西湖人超级多,建议早上6:30就出发,避开人流高峰,不然拍照全是人头!</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>出来后你就从天安门广场的地下通道到天安门城楼附近</t>
+          <t>节假日西湖人超级多</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>crowd</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>可以到天安门城楼上去看看，下来后你一直往里面走</t>
+          <t>建议早上6:30就出发,避开人流高峰,不然拍照全是人头!</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0003</t>
+          <t>西湖_travelog_2_adv_0001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>出来后你就从天安门广场的地下通道到天安门城楼附近,你可以到天安门城楼上去看看,下来后你一直往里面走,就是故宫的午门,沿着中轴线向北游览三大殿,从神武门出来,对面就是景山公园,从景山公园的西 起了个大早,飞机11:00左右到达北京机场,出机场坐了机场大巴,16元一张票.</t>
+          <t>想要获取完整的西湖人文景点讲解词、文史资料、小众打卡点位的朋友,可以给我发私信,也可以加我的交流:,我会把整理好的资料免费发给大家.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>就是故宫的午门</t>
+          <t>要获取完整的西湖人文景点讲解词、文史资料、小众打卡点位的朋友</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>route</t>
+          <t>other</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>可以到天安门城楼上去看看，下来后你一直往里面走，就是故宫的午门</t>
+          <t>可以给我发私信,也可以加我的交流:,我会把整理好的资料免费发给大家</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0004</t>
+          <t>西湖_travelog_2_adv_0002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>请推荐详细点的路线~酒店在天安门那边,想去长城,798,三里屯,故宫.</t>
+          <t>这条路线以人文景点为主,建议大家提前了解一下西湖的历史,逛的时候会更有代入感 2.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>详细点的路线~酒店在天安门那边</t>
+          <t>这条路线以人文景点为主</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>推荐详细点的路线~酒店在天安门那边,想去长城,798,三里屯,故宫</t>
+          <t>建议大家提前了解一下西湖的历史,逛的时候会更有代入感2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -683,158 +683,665 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0005</t>
+          <t>西湖_travelog_2_adv_0003</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>请指点下~ 我建议您分这样几天: 第一天,早起一点儿,上午游览故宫,如果是十一假期以后,从南门进,顺便看看天安门,大剧院,如果是十一期间,故宫好像有些地方不开放,你可以坐一站5路汽车从北门进,故宫最好多转转,珍宝馆是单收费的,不过看看挺不错的.</t>
+          <t>这条路线以人文景点为主,建议大家提前了解一下西湖的历史,逛的时候会更有代入感 2.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>十一假期以后</t>
+          <t>提前了解一下西湖的历史</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>time</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>可以坐一站5路汽车从北门进,故宫最好多转转,珍宝馆是单收费的,不过看看挺不错的</t>
+          <t>建议大家提前了解一下西湖的历史</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0006</t>
+          <t>西湖_travelog_2_adv_0004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>请指点下~ 我建议您分这样几天: 第一天,早起一点儿,上午游览故宫,如果是十一假期以后,从南门进,顺便看看天安门,大剧院,如果是十一期间,故宫好像有些地方不开放,你可以坐一站5路汽车从北门进,故宫最好多转转,珍宝馆是单收费的,不过看看挺不错的.</t>
+          <t>很多小众人文景点都免费开放,只需要提前预约就可以进去,大家一定要提前预约 早上8:00 我们从湖滨出发,步行20分钟就到了断桥残雪,早上的断桥人非常少,完全没有节假日的人头攒动,我们可以安安静静的感受断桥的历史.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>指点下~我</t>
+          <t>只需要提前预约就</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>time</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>建议您分这样几天:第一天，早起一点儿，上午游览故宫</t>
+          <t>可以进去，大家一定要提前预约早上8:00我们从湖滨出发，步行20分钟就到了断桥残雪</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>故宫_travelog_5_adv_0007</t>
+          <t>西湖_travelog_3_adv_0001</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>故宫</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>请指点下~ 我建议您分这样几天: 第一天,早起一点儿,上午游览故宫,如果是十一假期以后,从南门进,顺便看看天安门,大剧院,如果是十一期间,故宫好像有些地方不开放,你可以坐一站5路汽车从北门进,故宫最好多转转,珍宝馆是单收费的,不过看看挺不错的.</t>
+          <t>11:30:游船从三潭印月出发,航行15分钟至花港码头(11:45),步行5分钟至花港观鱼餐厅(11:50),用餐30分钟(11:50-12:20),人均60元(推荐西湖醋鱼、龙井虾仁),休整10分钟至12:30.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>十一</t>
+          <t>步行5分钟至花港观鱼餐厅(11</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>transport</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>可以坐一站5路汽车从北门进</t>
+          <t>推荐西湖醋鱼、龙井虾仁),休整10分钟至12:30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>黄山_travelog_5_adv_0001</t>
+          <t>西湖_travelog_4_adv_0001</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>黄山</t>
+          <t>西湖</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>不含玻璃栈道78元/人自理) 4,住宿:山下两晚商务酒店标准间(补单房差加160元/人/天×2天) 6,保险:旅行社责任险,建议购买旅游意外险20元/人</t>
+          <t>层级1(整体):3天2晚季节适配环线(基于官方路线优化,分摄影时段+季节分支) 层级2(每日结构):核心摄影段+休整段+小众季节分支段 层级3(时段细分):清晨/上午/中午/下午/傍晚,含停留时长+摄影建议+季节适配.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>山下两晚商务酒店标准间(补单房差加160元/人/天×2天)6</t>
+          <t>含停留时长+摄影</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>time_duration</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>建议购买旅游意外险20元/人</t>
+          <t>建议+季节适配</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>西湖_travelog_4_adv_0002</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>西湖</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>实际路线:摄影+季节层级(整体→每日摄影段→核心/休整/小众→时段/摄影建议/季节),按春季摄影黄金时段设计,增加小众机位和茶文化体验,适配深度游客.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>摄影+季节层级(整体→每日摄影段→核心/休整/小众→时段/摄影</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>建议/季节),按春季摄影黄金时段设计,增加小众机位和茶文化体验,适配深度游客</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>西湖_travelog_5_adv_0001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>西湖</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>购买游船票后,排队10分钟登船,它的船舱很宽敞,能坐50人,这里的座位靠窗的最好,因为它的视野无遮挡.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>排队10分钟登船</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>crowd</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>最好,因为它的视野无遮挡</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>张家界_travelog_1_adv_0001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>想要获取高清张家界路线图、避坑指南、私藏小众机位、本地美食推荐的朋友,可以加我电话:,邮箱:,免费发给大家!</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>要获取高清张家界路线图、避坑指南、私藏小众机位、本地美食</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>route</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>推荐的朋友,可以加我电话:,邮箱:,免费发给大家</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>张家界_travelog_1_adv_0002</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>索道:百龙天梯单程72元/人,天子山索道单程72元/人,黄石寨索道单程65元/人,十里画廊小火车单程38元/人,不想走路的可以直接冲!</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>走路的</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>可以直接冲</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>张家界_travelog_2_adv_0001</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>早上7:00 我们起床吃了早饭,从武陵源门票站入园,乘坐景区环保车前往水绕四门,车程10分钟,早上7:20抵达水绕四门,也就是金鞭溪的终点,我们今天选择反穿金鞭溪,从终点走到起点,这样可以避开人流,因为常规游客都是从起点往终点走,我们反着走,全程几乎看不到人,完全承包了整个金鞭溪!</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>早上7</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>可以避开人流,因为常规游客都是从起点往终点走,我们反着走,全程几乎看不到人,完全承包了整个金鞭溪!</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>张家界_travelog_2_adv_0002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>早上7:00 我们起床吃了早饭,从武陵源门票站入园,乘坐景区环保车前往水绕四门,车程10分钟,早上7:20抵达水绕四门,也就是金鞭溪的终点,我们今天选择反穿金鞭溪,从终点走到起点,这样可以避开人流,因为常规游客都是从起点往终点走,我们反着走,全程几乎看不到人,完全承包了整个金鞭溪!</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>今天选择反穿金鞭溪</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>可以避开人流</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
         <v>0.7</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>张家界_travelog_2_adv_0003</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>早上7:00 我们起床吃了早饭,从武陵源门票站入园,乘坐景区环保车前往水绕四门,车程10分钟,早上7:20抵达水绕四门,也就是金鞭溪的终点,我们今天选择反穿金鞭溪,从终点走到起点,这样可以避开人流,因为常规游客都是从起点往终点走,我们反着走,全程几乎看不到人,完全承包了整个金鞭溪!</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>从终点走到起点</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>可以避开人流，因为常规游客都是从起点往终点走</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>张家界_travelog_2_adv_0004</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>早上6:00 我们就起床了,前往老屋场看日出,老屋场是张家界看日出最好的地方,人特别少,完全没有常规景点的人头攒动,我们从民宿出发,步行1个小时,早上7:00抵达老屋场的观景台,刚好赶上了日出,橘红色的太阳从峰林后面慢慢升起来,整个天空都变成了金色,阳光洒在峰林和梯田上,真的太美了,我们所有人都被眼前的风景震撼到了,完全说不出话!</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>早上6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>最好的地方</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>张家界_travelog_2_adv_0005</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上午10:30 我们抵达黄石寨山顶,沿着环形步道走了一圈,全程步行2个小时,打卡了六奇阁、摘星台、五指峰、天桥遗墩所有核心景点,我们去的时候,旅行团都已经走了,人特别少,我们可以安安静静的看风景,黄石寨的观景台真的绝了,可以360度看张家界的峰林全景,真的太震撼了 中午12:30 我们在黄石寨山顶的补给点吃了午饭,是提前带的自热米饭和零食,休息了1个小时,下午13:30我们选择从黄石寨的后山步道下山,前往琵琶溪,这条路线是小众的徒步路线,全程4公里,都是下坡,人特别少,沿途的风景特别原始,我们走了1个半小时,下午15:00抵达琵琶溪.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>的太震撼了中午12:30我们</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>可以360度看张家界的峰林全景，真的太震撼了中午12:30我们在黄石寨山顶的补给点吃了午饭，是提前带的自热米饭和零食</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>张家界_travelog_3_adv_0001</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12:00:从天子山索道上站出发,步行10分钟至天子山餐厅(12:10),用餐40分钟(12:10-12:50),人均50元(推荐三下锅、葛根粉),休整10分钟至13:00.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>步行10分钟至天子山餐厅(12</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>推荐三下锅、葛根粉),休整10分钟至13:00</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>张家界_travelog_4_adv_0001</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>层级1(整体):3天2晚恐高适配环线(基于官方路线优化,分观景时段+恐高分支) 层级2(每日结构):核心观景段+休整段+小众恐高分支段 层级3(时段细分):清晨/上午/中午/下午/傍晚,含停留时长+恐高建议+观景时段.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>含停留时长+恐高</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>time_duration</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>建议+观景时段</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>张家界_travelog_5_adv_0001</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>水绕四门的旁边是百龙天梯,它是世界最高的户外电梯,这里的运行高度有335米,它的速度很快,66秒就能到顶,要是你恐高,不建议坐它.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>你恐高</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>建议坐它</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>张家界_travelog_5_adv_0002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>张家界</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>走在天下第一桥上,它的护栏是铁制的,这里的风很大,吹得护栏晃动,要是你恐高,不要靠近它的边缘,它的下面是万丈深渊.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>你恐高</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>不要靠近它的边缘,它的下面是万丈深渊</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
